--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486705_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486705_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.54</v>
+        <v>7.4804</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2022</v>
+        <v>5.2916</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3378</v>
+        <v>2.1888</v>
       </c>
       <c r="G2" t="n">
         <v>7.9588</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.237</v>
+        <v>0.7034</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6898</v>
+        <v>0.3996</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4528</v>
+        <v>0.3039</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>C. TEASLEY JR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5085</v>
+        <v>3.641</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0884</v>
+        <v>2.3664</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4202</v>
+        <v>1.2746</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7089</v>
+        <v>4.1169</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0277</v>
+        <v>0.8683</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3188</v>
+        <v>3.2486</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0405</v>
+        <v>3.4906</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9591</v>
+        <v>0.8004</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0814</v>
+        <v>2.6903</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3316</v>
+        <v>0.6263</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0679</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4002</v>
+        <v>0.5583</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3129</v>
+        <v>0.7518</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0479</v>
+        <v>0.8065</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2651</v>
+        <v>-0.0548</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. TEASLEY JR</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2811</v>
+        <v>2.4577</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0561</v>
+        <v>2.261</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2249</v>
+        <v>0.1967</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1169</v>
+        <v>1.7089</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8683</v>
+        <v>2.0277</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2486</v>
+        <v>-0.3188</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4906</v>
+        <v>2.0405</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8004</v>
+        <v>1.9591</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6903</v>
+        <v>0.0814</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6263</v>
+        <v>-0.3316</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0679</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5583</v>
+        <v>-0.4002</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3919</v>
+        <v>0.2621</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4963</v>
+        <v>0.2205</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1044</v>
+        <v>0.0416</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0348</v>
+        <v>1.0599</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2473</v>
+        <v>2.3717</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2125</v>
+        <v>-1.3118</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2829</v>
@@ -844,13 +844,13 @@
         <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4987</v>
+        <v>1.5238</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0129</v>
+        <v>1.1373</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4858</v>
+        <v>0.3865</v>
       </c>
       <c r="V5" t="n">
         <v>-2.498</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3744</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1666</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2079</v>
+        <v>0.6232</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1898</v>
+        <v>0.1305</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8479</v>
+        <v>-0.1523</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0377</v>
+        <v>0.2828</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7494</v>
+        <v>1.2699</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0886</v>
+        <v>0.1936</v>
       </c>
       <c r="L6" t="n">
-        <v>1.838</v>
+        <v>1.0763</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5596</v>
+        <v>-1.1395</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7593</v>
+        <v>-0.3459</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8003</v>
+        <v>-0.7935</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3515</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8962</v>
+        <v>-4.827</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5446</v>
+        <v>2.7031</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1582</v>
+        <v>0.3655</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3511</v>
+        <v>0.4065</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1929</v>
+        <v>-0.041</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3709</v>
+        <v>1.5559</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3709</v>
+        <v>2.4554</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9576</v>
+        <v>-1.0225</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3537</v>
+        <v>-0.9388</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6039</v>
+        <v>-0.0837</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1021</v>
+        <v>0.1898</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8143</v>
+        <v>-0.8479</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2878</v>
+        <v>1.0377</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0233</v>
+        <v>1.7494</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4279</v>
+        <v>-0.0886</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4046</v>
+        <v>1.838</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1253</v>
+        <v>-1.5596</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2422</v>
+        <v>-0.7593</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8832</v>
+        <v>-0.8003</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8589</v>
+        <v>0.5101</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2682</v>
+        <v>0.5789</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5906</v>
+        <v>-0.0687</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2814</v>
+        <v>-1.6137</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6811</v>
+        <v>-1.0419</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3997</v>
+        <v>-0.5718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1305</v>
+        <v>-1.7871</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1523</v>
+        <v>-0.876</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2828</v>
+        <v>-0.911</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2699</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1936</v>
+        <v>-0.2549</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0763</v>
+        <v>-0.6488</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1395</v>
+        <v>-0.8833</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3459</v>
+        <v>-0.6211</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7935</v>
+        <v>-0.2623</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.827</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7031</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8439</v>
+        <v>-0.0277</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5795</v>
+        <v>-0.1381</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2645</v>
+        <v>0.1104</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5559</v>
+        <v>-0.5712</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8995</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2316</v>
+        <v>-1.7271</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5107</v>
+        <v>-0.9742</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7208</v>
+        <v>-0.7529</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7871</v>
+        <v>-3.1021</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.876</v>
+        <v>-0.8143</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.911</v>
+        <v>-2.2878</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2549</v>
+        <v>0.4279</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>-0.4046</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8833</v>
+        <v>-3.1253</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6211</v>
+        <v>-1.2422</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2623</v>
+        <v>-1.8832</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6456</v>
+        <v>1.0893</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.607</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0386</v>
+        <v>0.4416</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7446</v>
+        <v>-5.153</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9315</v>
+        <v>-1.4144</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.8131</v>
+        <v>-3.7386</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6215</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6677</v>
+        <v>-0.0761</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>-0.2003</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.774800000000001</v>
+        <v>5.050800000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>6.950400000000002</v>
+        <v>7.226299999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.175599999999999</v>
+        <v>-2.1755</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3113</v>
+        <v>4.311300000000002</v>
       </c>
       <c r="H11" t="n">
         <v>0.3435999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>3.967900000000001</v>
+        <v>3.967900000000002</v>
       </c>
       <c r="J11" t="n">
         <v>16.8381</v>
       </c>
       <c r="K11" t="n">
-        <v>6.901899999999999</v>
+        <v>6.9019</v>
       </c>
       <c r="L11" t="n">
         <v>9.936300000000001</v>
@@ -1297,13 +1297,13 @@
         <v>-12.5267</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.558300000000001</v>
+        <v>-6.5583</v>
       </c>
       <c r="O11" t="n">
         <v>-5.9685</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9655</v>
+        <v>-0.9654999999999996</v>
       </c>
       <c r="Q11" t="n">
         <v>-16.4118</v>
@@ -1312,13 +1312,13 @@
         <v>15.4462</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8264</v>
+        <v>5.1022</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5827</v>
+        <v>3.8586</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2436</v>
+        <v>1.2437</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3975</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3573</v>
+        <v>5.994</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8514</v>
+        <v>5.7331</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5059</v>
+        <v>0.2609</v>
       </c>
       <c r="G12" t="n">
-        <v>5.16</v>
+        <v>7.1478</v>
       </c>
       <c r="H12" t="n">
-        <v>2.393</v>
+        <v>4.4553</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767</v>
+        <v>2.6925</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3067</v>
+        <v>7.0524</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3596</v>
+        <v>4.525</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9471</v>
+        <v>2.5275</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1467</v>
+        <v>0.0953</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9665</v>
+        <v>-0.0697</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1802</v>
+        <v>0.165</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R12" t="n">
-        <v>3.0892</v>
+        <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3478</v>
+        <v>-0.1377</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4409</v>
+        <v>-0.1794</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0931</v>
+        <v>0.0417</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6565</v>
+        <v>0.5286</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7563</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3265</v>
+        <v>5.858</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5263</v>
+        <v>4.4377</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1998</v>
+        <v>1.4203</v>
       </c>
       <c r="G13" t="n">
-        <v>7.1478</v>
+        <v>5.16</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4553</v>
+        <v>2.393</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6925</v>
+        <v>2.767</v>
       </c>
       <c r="J13" t="n">
-        <v>7.0524</v>
+        <v>7.3067</v>
       </c>
       <c r="K13" t="n">
-        <v>4.525</v>
+        <v>3.3596</v>
       </c>
       <c r="L13" t="n">
-        <v>2.5275</v>
+        <v>3.9471</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0953</v>
+        <v>-2.1467</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0697</v>
+        <v>-0.9665</v>
       </c>
       <c r="O13" t="n">
-        <v>0.165</v>
+        <v>-1.1802</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3515</v>
+        <v>3.0892</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8052</v>
+        <v>-0.1515</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3863</v>
+        <v>0.0272</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.419</v>
+        <v>-0.1787</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5286</v>
+        <v>0.6565</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7563</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0195</v>
+        <v>1.2044</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8177</v>
+        <v>1.3006</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2018</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0037</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0151</v>
+        <v>0.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6616</v>
+        <v>0.1445</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3535</v>
+        <v>0.0555</v>
       </c>
       <c r="V14" t="n">
         <v>0.6565</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0109</v>
+        <v>-0.1102</v>
       </c>
       <c r="E15" t="n">
         <v>-0.7447</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7337</v>
+        <v>0.6344</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5516</v>
@@ -1624,13 +1624,13 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1545</v>
+        <v>0.0552</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2097</v>
+        <v>0.1104</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4222</v>
+        <v>-1.9989</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9087</v>
+        <v>1.219</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3309</v>
+        <v>-3.2179</v>
       </c>
       <c r="G16" t="n">
         <v>-2.6308</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5059</v>
+        <v>-1.0825</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7174</v>
+        <v>-0.4071</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7885</v>
+        <v>-0.6754</v>
       </c>
       <c r="V16" t="n">
         <v>0.9421</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.5861</v>
+        <v>-2.3986</v>
       </c>
       <c r="E17" t="n">
         <v>0.0581</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6443</v>
+        <v>-2.4567</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7437</v>
@@ -1780,13 +1780,13 @@
         <v>2.7031</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6494</v>
+        <v>-1.4619</v>
       </c>
       <c r="T17" t="n">
         <v>-0.359</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2904</v>
+        <v>-1.1029</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9319</v>
+        <v>-3.2036</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4063</v>
+        <v>-1.7166</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5257</v>
+        <v>-1.4871</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9003</v>
@@ -1858,13 +1858,13 @@
         <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3199</v>
+        <v>0.0482</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3857</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0272</v>
       </c>
       <c r="V18" t="n">
         <v>0.6138</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.0071</v>
+        <v>-4.4237</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0917</v>
+        <v>-3.7814</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9154</v>
+        <v>-0.6423</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7548</v>
@@ -1936,13 +1936,13 @@
         <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6384</v>
+        <v>-1.055</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7174</v>
+        <v>-0.4071</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9211</v>
+        <v>-0.6479</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5197</v>
+        <v>-5.0067</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7439</v>
+        <v>-4.3302</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7758</v>
+        <v>-0.6765</v>
       </c>
       <c r="G20" t="n">
         <v>-5.0342</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0647</v>
+        <v>-0.5517</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4966</v>
+        <v>-0.083</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5681</v>
+        <v>-0.4688</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7746</v>
+        <v>-4.085299999999998</v>
       </c>
       <c r="E21" t="n">
-        <v>2.175600000000001</v>
+        <v>2.175599999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.9505</v>
+        <v>-6.2611</v>
       </c>
       <c r="G21" t="n">
         <v>-4.311299999999999</v>
@@ -2092,13 +2092,13 @@
         <v>16.4115</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.8263</v>
+        <v>-4.1369</v>
       </c>
       <c r="T21" t="n">
         <v>-1.2437</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.5827</v>
+        <v>-2.8933</v>
       </c>
       <c r="V21" t="n">
         <v>3.3975</v>
